--- a/resources/templates/cooperation_agreement-bulk-template.xlsx
+++ b/resources/templates/cooperation_agreement-bulk-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,69 +449,84 @@
         <v>transportAllowance</v>
       </c>
       <c r="Q1" t="str">
+        <v>transportAllowanceUnit</v>
+      </c>
+      <c r="R1" t="str">
         <v>mealAllowance</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
+        <v>mealAllowanceUnit</v>
+      </c>
+      <c r="T1" t="str">
         <v>phoneAllowance</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
+        <v>phoneAllowanceUnit</v>
+      </c>
+      <c r="V1" t="str">
         <v>operationalCostAllowance</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
+        <v>operationalCostAllowanceUnit</v>
+      </c>
+      <c r="X1" t="str">
         <v>tlAllowance</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Y1" t="str">
+        <v>tlAllowanceUnit</v>
+      </c>
+      <c r="Z1" t="str">
         <v>partnerBankAccountNumber</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AA1" t="str">
         <v>partnerBankAccountName</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AB1" t="str">
         <v>partnerBankName</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AC1" t="str">
         <v>agreementDuration</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AD1" t="str">
         <v>workHoursPerDay</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AE1" t="str">
         <v>placementArea</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AF1" t="str">
         <v>picName</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AG1" t="str">
         <v>picTitle</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AH1" t="str">
         <v>picEmail</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AI1" t="str">
         <v>picAddress</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AJ1" t="str">
         <v>letterDate</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AK1" t="str">
         <v>location</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AL1" t="str">
         <v>directorSignatureUrl</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AM1" t="str">
         <v>partnerSignatureUrl</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AN1" t="str">
         <v>email</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AO1" t="str">
         <v>callback_url</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AP1" t="str">
         <v>callback_header</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AQ1" t="str">
         <v>data_json</v>
       </c>
     </row>
@@ -562,78 +577,93 @@
         <v>5000000</v>
       </c>
       <c r="P2">
+        <v>45000</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>hari</v>
+      </c>
+      <c r="R2">
+        <v>300000</v>
+      </c>
+      <c r="S2" t="str">
+        <v>per bulan</v>
+      </c>
+      <c r="T2">
         <v>100000</v>
       </c>
-      <c r="Q2">
-        <v>300000</v>
-      </c>
-      <c r="R2">
-        <v>100000</v>
-      </c>
-      <c r="S2">
+      <c r="U2" t="str">
+        <v>bulan</v>
+      </c>
+      <c r="V2">
         <v>250000</v>
       </c>
-      <c r="T2">
+      <c r="W2" t="str">
+        <v>per bulan</v>
+      </c>
+      <c r="X2">
         <v>150000</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Y2" t="str">
+        <v>minggu</v>
+      </c>
+      <c r="Z2" t="str">
         <v>1234567890</v>
       </c>
-      <c r="V2" t="str">
+      <c r="AA2" t="str">
         <v>Nama Mitra</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AB2" t="str">
         <v>BCA</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>6</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>8</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AE2" t="str">
         <v>Jakarta</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AF2" t="str">
         <v>Nama PIC</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AG2" t="str">
         <v>PIC Area</v>
       </c>
-      <c r="AC2" t="str">
+      <c r="AH2" t="str">
         <v>pic@example.com</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AI2" t="str">
         <v>Jl. PIC No. 1, Jakarta</v>
       </c>
-      <c r="AE2" t="str">
+      <c r="AJ2" t="str">
         <v>2026-07-07</v>
       </c>
-      <c r="AF2" t="str">
+      <c r="AK2" t="str">
         <v>Jakarta</v>
       </c>
-      <c r="AG2" t="str">
+      <c r="AL2" t="str">
         <v/>
       </c>
-      <c r="AH2" t="str">
+      <c r="AM2" t="str">
         <v/>
       </c>
-      <c r="AI2" t="str">
+      <c r="AN2" t="str">
         <v>penerima@example.com</v>
       </c>
-      <c r="AJ2" t="str">
+      <c r="AO2" t="str">
         <v/>
       </c>
-      <c r="AK2" t="str">
+      <c r="AP2" t="str">
         <v>{}</v>
       </c>
-      <c r="AL2" t="str">
+      <c r="AQ2" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AQ2"/>
   </ignoredErrors>
 </worksheet>
 </file>